--- a/Raspisanie_Osень_Fit.xlsx
+++ b/Raspisanie_Osень_Fit.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +57,10 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0016A34A"/>
     </font>
     <font>
       <color rgb="00DC2626"/>
@@ -115,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -154,7 +158,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2762,7 +2767,7 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
@@ -2814,47 +2819,47 @@
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>2016-2017 Высшая 5×5 — группы 5×4</t>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>Группа D</t>
+          <t>Группа B</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="I45" s="9" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>Огонь 5</t>
+          <t>Молот</t>
         </is>
       </c>
       <c r="K45" s="9" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Цыганов</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2881,7 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
@@ -2886,28 +2891,32 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr"/>
+          <t>2016-2017 Высшая 5×5 — группы 5×4</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>Группа D</t>
+        </is>
+      </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>Смена-Кошелев</t>
+          <t>Огонь 5</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -2929,7 +2938,7 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
@@ -2939,28 +2948,28 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Смена-Кошелев</t>
         </is>
       </c>
       <c r="K47" s="9" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
@@ -2982,42 +2991,38 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>Группа A</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr"/>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Галимуллин</t>
         </is>
       </c>
       <c r="J48" s="8" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>Женя</t>
+          <t>Тетерин</t>
         </is>
       </c>
     </row>
@@ -3034,43 +3039,47 @@
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>Группа A</t>
+        </is>
+      </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>Красные опасные</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="I49" s="9" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Смолкин</t>
         </is>
       </c>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="K49" s="9" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Женя</t>
         </is>
       </c>
     </row>
@@ -3087,43 +3096,47 @@
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="J50" s="8" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Лысиков</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3158,7 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
@@ -3155,28 +3168,28 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Красные опасные</t>
         </is>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -3198,64 +3211,60 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>Группа A</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr"/>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>Комета</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>Женя</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J52" s="8" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>04.10</t>
+          <t>03.10</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
@@ -3265,134 +3274,142 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="I53" s="9" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Галимуллин</t>
         </is>
       </c>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>Красные опасные</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="K53" s="9" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>04.10</t>
+          <t>03.10</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Группа A</t>
+        </is>
+      </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Женя</t>
         </is>
       </c>
       <c r="J54" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Тетерин</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>04.10</t>
+          <t>03.10</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Седин</t>
         </is>
       </c>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>Школа 1</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="K55" s="9" t="inlineStr">
         <is>
-          <t>Галимуллин</t>
+          <t>Лысиков</t>
         </is>
       </c>
     </row>
@@ -3414,42 +3431,38 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="inlineStr"/>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="I56" s="9" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="J56" s="8" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>Красные опасные</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>Цыганов</t>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3479,12 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
@@ -3487,22 +3500,22 @@
       <c r="G57" s="7" t="inlineStr"/>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>Красные опасные 2</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J57" s="8" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="K57" s="9" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Щадин</t>
         </is>
       </c>
     </row>
@@ -3519,12 +3532,12 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
@@ -3540,12 +3553,12 @@
       <c r="G58" s="7" t="inlineStr"/>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Смолкин</t>
         </is>
       </c>
       <c r="J58" s="8" t="inlineStr">
@@ -3572,43 +3585,47 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>Смена-Кошелев</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="I59" s="9" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Седин</t>
         </is>
       </c>
       <c r="J59" s="8" t="inlineStr">
         <is>
-          <t>Спутник-1</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="K59" s="9" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
     </row>
@@ -3625,12 +3642,12 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
@@ -3650,22 +3667,22 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 175/96</t>
         </is>
       </c>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Лысиков</t>
         </is>
       </c>
       <c r="J60" s="8" t="inlineStr">
         <is>
-          <t>Школа 175/96</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>Лысиков</t>
+          <t>Якимов</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3699,7 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -3703,22 +3720,22 @@
       <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="8" t="inlineStr">
         <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J61" s="8" t="inlineStr">
+        <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I61" s="9" t="inlineStr">
+      <c r="K61" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
-        </is>
-      </c>
-      <c r="J61" s="8" t="inlineStr">
-        <is>
-          <t>Красные опасные 3</t>
-        </is>
-      </c>
-      <c r="K61" s="9" t="inlineStr">
-        <is>
-          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3752,7 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -3756,22 +3773,22 @@
       <c r="G62" s="7" t="inlineStr"/>
       <c r="H62" s="8" t="inlineStr">
         <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+      <c r="J62" s="8" t="inlineStr">
+        <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
+      <c r="K62" s="9" t="inlineStr">
         <is>
           <t>Галимуллин</t>
-        </is>
-      </c>
-      <c r="J62" s="8" t="inlineStr">
-        <is>
-          <t>Акулы 42/11</t>
-        </is>
-      </c>
-      <c r="K62" s="9" t="inlineStr">
-        <is>
-          <t>Щадин</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3805,7 @@
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -3803,13 +3820,13 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Смена-Кошелев</t>
         </is>
       </c>
       <c r="I63" s="9" t="inlineStr">
@@ -3819,12 +3836,12 @@
       </c>
       <c r="J63" s="8" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Спутник-1</t>
         </is>
       </c>
       <c r="K63" s="9" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Агарков</t>
         </is>
       </c>
     </row>
@@ -3841,12 +3858,12 @@
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
@@ -3866,12 +3883,12 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Олимп</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>Седин</t>
+          <t>Якимов</t>
         </is>
       </c>
       <c r="J64" s="8" t="inlineStr">
@@ -3888,128 +3905,132 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
+          <t>Поле 7*7 #2</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>7*7</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>Группа C</t>
+        </is>
+      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Смена-Ведиси</t>
+        </is>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>Куликов</t>
+        </is>
+      </c>
+      <c r="J65" s="8" t="inlineStr">
+        <is>
+          <t>Галатасарай</t>
+        </is>
+      </c>
+      <c r="K65" s="9" t="inlineStr">
+        <is>
+          <t>Лысиков</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="16" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>04.10</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="8" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="I66" s="9" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>Красные опасные 2</t>
-        </is>
-      </c>
-      <c r="K65" s="9" t="inlineStr">
+      <c r="J66" s="8" t="inlineStr">
+        <is>
+          <t>Красные опасные 3</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="inlineStr">
         <is>
           <t>Анисимов</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>10.10</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="D66" s="4" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #2</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F66" s="4" t="inlineStr">
-        <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="inlineStr"/>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>Галимуллин</t>
-        </is>
-      </c>
-      <c r="J66" s="5" t="inlineStr">
-        <is>
-          <t>Киты 42/11</t>
-        </is>
-      </c>
-      <c r="K66" s="6" t="inlineStr">
-        <is>
-          <t>Щадин</t>
         </is>
       </c>
     </row>
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C67" s="7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
@@ -4025,185 +4046,189 @@
       <c r="G67" s="7" t="inlineStr"/>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Школа 1</t>
         </is>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Галимуллин</t>
         </is>
       </c>
       <c r="J67" s="8" t="inlineStr">
         <is>
-          <t>Школа 64/92</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="K67" s="9" t="inlineStr">
         <is>
-          <t>Тетерин</t>
+          <t>Щадин</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr"/>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>Смена КС (К)</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>Якимов</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J68" s="8" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Смолкин</t>
         </is>
       </c>
     </row>
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Группа C</t>
+        </is>
+      </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>Красные опасные 3</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="I69" s="9" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Уразаков</t>
         </is>
       </c>
       <c r="J69" s="8" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Галатасарай</t>
         </is>
       </c>
       <c r="K69" s="9" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Лысиков</t>
         </is>
       </c>
     </row>
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>10.10</t>
+          <t>04.10</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 7*7 #2</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G70" s="7" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Группа B</t>
+        </is>
+      </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Смена КС (К)</t>
         </is>
       </c>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Якимов</t>
         </is>
       </c>
       <c r="J70" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Олимп</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Седин</t>
         </is>
       </c>
     </row>
@@ -4220,12 +4245,12 @@
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
@@ -4241,132 +4266,128 @@
       <c r="G71" s="7" t="inlineStr"/>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="I71" s="9" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Беляев</t>
         </is>
       </c>
       <c r="J71" s="8" t="inlineStr">
         <is>
+          <t>Красные опасные 2</t>
+        </is>
+      </c>
+      <c r="K71" s="9" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr"/>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Киты 42/11</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="K71" s="9" t="inlineStr">
+      <c r="I73" s="9" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
       </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>10.10</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C72" s="7" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
-        <is>
-          <t>Седин</t>
-        </is>
-      </c>
-      <c r="J72" s="8" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="K72" s="9" t="inlineStr">
-        <is>
-          <t>Лысиков</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>10.10</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #1</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
-        </is>
-      </c>
-      <c r="G73" s="4" t="inlineStr"/>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>Беляев</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>Крепыши 3</t>
-        </is>
-      </c>
-      <c r="K73" s="6" t="inlineStr">
-        <is>
-          <t>Анисимов</t>
+      <c r="J73" s="8" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="K73" s="9" t="inlineStr">
+        <is>
+          <t>Тетерин</t>
         </is>
       </c>
     </row>
@@ -4383,43 +4404,47 @@
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>7*7</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G74" s="7" t="inlineStr"/>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>Группа C</t>
+        </is>
+      </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Школа 139</t>
         </is>
       </c>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Гурин</t>
         </is>
       </c>
       <c r="J74" s="8" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Смена-Ведиси</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Куликов</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4461,12 @@
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
@@ -4457,22 +4482,22 @@
       <c r="G75" s="7" t="inlineStr"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Красные опасные 3</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Анисимов</t>
         </is>
       </c>
       <c r="J75" s="8" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="K75" s="9" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -4489,281 +4514,281 @@
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr"/>
+      <c r="H76" s="8" t="inlineStr">
+        <is>
+          <t>68 школа</t>
+        </is>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>Шкреба</t>
+        </is>
+      </c>
+      <c r="J76" s="8" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #3</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>Кузьмичев</t>
+        </is>
+      </c>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="K77" s="9" t="inlineStr">
+        <is>
+          <t>Майоров</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="7" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>Поле 7*7 #1</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>7*7</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>Группа C</t>
+        </is>
+      </c>
+      <c r="H78" s="8" t="inlineStr">
+        <is>
+          <t>Крылья дубль-школа №7</t>
+        </is>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>Уразаков</t>
+        </is>
+      </c>
+      <c r="J78" s="8" t="inlineStr">
+        <is>
+          <t>Школа 139</t>
+        </is>
+      </c>
+      <c r="K78" s="9" t="inlineStr">
+        <is>
+          <t>Гурин</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
-      <c r="H76" s="8" t="inlineStr">
-        <is>
-          <t>Школа 175/96</t>
-        </is>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>Лысиков</t>
-        </is>
-      </c>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="K76" s="9" t="inlineStr">
-        <is>
-          <t>Якимов</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Поле 4*4 #1</t>
-        </is>
-      </c>
-      <c r="E77" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F77" s="10" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
-      <c r="G77" s="10" t="inlineStr"/>
-      <c r="H77" s="11" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr"/>
+      <c r="H79" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I77" s="12" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J77" s="11" t="inlineStr">
-        <is>
-          <t>Крепыши</t>
-        </is>
-      </c>
-      <c r="K77" s="12" t="inlineStr">
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C78" s="10" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>Поле 4*4 #2</t>
-        </is>
-      </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F78" s="10" t="inlineStr">
-        <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
-        </is>
-      </c>
-      <c r="G78" s="10" t="inlineStr"/>
-      <c r="H78" s="11" t="inlineStr">
-        <is>
-          <t>Киты 42/11</t>
-        </is>
-      </c>
-      <c r="I78" s="12" t="inlineStr">
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>10.10</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G80" s="7" t="inlineStr"/>
+      <c r="H80" s="8" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="I80" s="9" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J78" s="11" t="inlineStr">
+      <c r="J80" s="8" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K78" s="12" t="inlineStr">
+      <c r="K80" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B79" s="10" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C79" s="10" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
-        <is>
-          <t>Поле 4*4 #3</t>
-        </is>
-      </c>
-      <c r="E79" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F79" s="10" t="inlineStr">
-        <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G79" s="10" t="inlineStr"/>
-      <c r="H79" s="11" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="I79" s="12" t="inlineStr">
-        <is>
-          <t>Тетерин</t>
-        </is>
-      </c>
-      <c r="J79" s="11" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="K79" s="12" t="inlineStr">
-        <is>
-          <t>Майоров</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #1</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
-        </is>
-      </c>
-      <c r="G80" s="4" t="inlineStr"/>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>Спутник</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>Агарков</t>
-        </is>
-      </c>
-      <c r="J80" s="5" t="inlineStr">
-        <is>
-          <t>Школа 1</t>
-        </is>
-      </c>
-      <c r="K80" s="6" t="inlineStr">
-        <is>
-          <t>Галимуллин</t>
         </is>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4779,44 +4804,44 @@
       <c r="G81" s="7" t="inlineStr"/>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Смолкин</t>
         </is>
       </c>
       <c r="J81" s="8" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="K81" s="9" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>11.10</t>
+          <t>10.10</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Сб</t>
+          <t>Пт</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -4846,12 +4871,12 @@
       </c>
       <c r="J82" s="8" t="inlineStr">
         <is>
-          <t>Галатасарай</t>
+          <t>Крылья дубль-школа №7</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
         <is>
-          <t>Лысиков</t>
+          <t>Уразаков</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4893,7 @@
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
@@ -4889,7 +4914,7 @@
       <c r="G83" s="10" t="inlineStr"/>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Профики 2</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
@@ -4899,7 +4924,7 @@
       </c>
       <c r="J83" s="11" t="inlineStr">
         <is>
-          <t>Крепыши 3</t>
+          <t>Крепыши</t>
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr">
@@ -4921,7 +4946,7 @@
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
@@ -4936,13 +4961,13 @@
       </c>
       <c r="F84" s="10" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr"/>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Киты 42/11</t>
         </is>
       </c>
       <c r="I84" s="12" t="inlineStr">
@@ -4952,12 +4977,12 @@
       </c>
       <c r="J84" s="11" t="inlineStr">
         <is>
-          <t>Спутник-1</t>
+          <t>68 школа</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Шкреба</t>
         </is>
       </c>
     </row>
@@ -4974,7 +4999,7 @@
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
@@ -4995,73 +5020,73 @@
       <c r="G85" s="10" t="inlineStr"/>
       <c r="H85" s="11" t="inlineStr">
         <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>Тетерин</t>
+        </is>
+      </c>
+      <c r="J85" s="11" t="inlineStr">
+        <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="I85" s="12" t="inlineStr">
+      <c r="K85" s="12" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
       </c>
-      <c r="J85" s="11" t="inlineStr">
-        <is>
-          <t>КС 26</t>
-        </is>
-      </c>
-      <c r="K85" s="12" t="inlineStr">
-        <is>
-          <t>Кузьмичев</t>
-        </is>
-      </c>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="D86" s="7" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>Поле 5*5 #1</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F86" s="7" t="inlineStr">
-        <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G86" s="7" t="inlineStr"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>Тетерин</t>
-        </is>
-      </c>
-      <c r="J86" s="8" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr"/>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Спутник</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K86" s="9" t="inlineStr">
+      <c r="K86" s="6" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
@@ -5080,7 +5105,7 @@
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -5095,85 +5120,81 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr"/>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Молот</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="I87" s="9" t="inlineStr">
         <is>
-          <t>Цыганов</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
       <c r="J87" s="8" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="K87" s="9" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Смолкин</t>
         </is>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="7" t="inlineStr">
+      <c r="A88" s="10" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B88" s="7" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C88" s="7" t="inlineStr">
+      <c r="C88" s="10" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D88" s="7" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F88" s="7" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>Крылья дубль-школа №7</t>
-        </is>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>Уразаков</t>
-        </is>
-      </c>
-      <c r="J88" s="8" t="inlineStr">
-        <is>
-          <t>Галатасарай</t>
-        </is>
-      </c>
-      <c r="K88" s="9" t="inlineStr">
-        <is>
-          <t>Лысиков</t>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E88" s="10" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F88" s="10" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr"/>
+      <c r="H88" s="11" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J88" s="11" t="inlineStr">
+        <is>
+          <t>Крепыши 3</t>
+        </is>
+      </c>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -5190,12 +5211,12 @@
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Поле 4*4 #1</t>
+          <t>Поле 4*4 #2</t>
         </is>
       </c>
       <c r="E89" s="10" t="inlineStr">
@@ -5205,28 +5226,28 @@
       </c>
       <c r="F89" s="10" t="inlineStr">
         <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr"/>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Профики 2</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J89" s="11" t="inlineStr">
         <is>
-          <t>Крепыши</t>
+          <t>Спутник-1</t>
         </is>
       </c>
       <c r="K89" s="12" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Агарков</t>
         </is>
       </c>
     </row>
@@ -5243,12 +5264,12 @@
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Поле 4*4 #2</t>
+          <t>Поле 4*4 #3</t>
         </is>
       </c>
       <c r="E90" s="10" t="inlineStr">
@@ -5258,81 +5279,81 @@
       </c>
       <c r="F90" s="10" t="inlineStr">
         <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr"/>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Спутник-1</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>КС 26</t>
         </is>
       </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Кузьмичев</t>
         </is>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="10" t="inlineStr">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B91" s="10" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D91" s="10" t="inlineStr">
-        <is>
-          <t>Поле 4*4 #3</t>
-        </is>
-      </c>
-      <c r="E91" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F91" s="10" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G91" s="10" t="inlineStr"/>
-      <c r="H91" s="11" t="inlineStr">
-        <is>
-          <t>Школа 35</t>
-        </is>
-      </c>
-      <c r="I91" s="12" t="inlineStr">
-        <is>
-          <t>Колюжный</t>
-        </is>
-      </c>
-      <c r="J91" s="11" t="inlineStr">
-        <is>
-          <t>Дружба</t>
-        </is>
-      </c>
-      <c r="K91" s="12" t="inlineStr">
-        <is>
-          <t>Майоров</t>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>Школа 64/92</t>
+        </is>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>Тетерин</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
+        <is>
+          <t>Школа 1</t>
+        </is>
+      </c>
+      <c r="K91" s="9" t="inlineStr">
+        <is>
+          <t>Галимуллин</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5370,12 @@
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -5370,207 +5391,203 @@
       <c r="G92" s="7" t="inlineStr"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
+          <t>Молот</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>Цыганов</t>
+        </is>
+      </c>
+      <c r="J92" s="8" t="inlineStr">
+        <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I92" s="9" t="inlineStr">
+      <c r="K92" s="9" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J92" s="8" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="K92" s="9" t="inlineStr">
-        <is>
-          <t>Женя</t>
-        </is>
-      </c>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="7" t="inlineStr">
+      <c r="A93" s="10" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="B93" s="10" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C93" s="7" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D93" s="7" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #2</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F93" s="7" t="inlineStr">
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #1</t>
+        </is>
+      </c>
+      <c r="E93" s="10" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F93" s="10" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr"/>
+      <c r="H93" s="11" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>Беляев</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="inlineStr">
+        <is>
+          <t>Крепыши</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="10" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C94" s="10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D94" s="10" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #2</t>
+        </is>
+      </c>
+      <c r="E94" s="10" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F94" s="10" t="inlineStr">
+        <is>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr"/>
+      <c r="H94" s="11" t="inlineStr">
+        <is>
+          <t>Спутник-1</t>
+        </is>
+      </c>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>Агарков</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="inlineStr">
+        <is>
+          <t>Щадин</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>11.10</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Сб</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="D95" s="10" t="inlineStr">
+        <is>
+          <t>Поле 4*4 #3</t>
+        </is>
+      </c>
+      <c r="E95" s="10" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F95" s="10" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>Школа 16</t>
-        </is>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>Смолкин</t>
-        </is>
-      </c>
-      <c r="J93" s="8" t="inlineStr">
-        <is>
-          <t>Школа 64/92</t>
-        </is>
-      </c>
-      <c r="K93" s="9" t="inlineStr">
-        <is>
-          <t>Тетерин</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>11.10</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t>Сб</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="D94" s="7" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E94" s="7" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>Группа B</t>
-        </is>
-      </c>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>Смена КС (К)</t>
-        </is>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>Якимов</t>
-        </is>
-      </c>
-      <c r="J94" s="8" t="inlineStr">
-        <is>
-          <t>Олимп</t>
-        </is>
-      </c>
-      <c r="K94" s="9" t="inlineStr">
-        <is>
-          <t>Седин</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
-        <is>
-          <t>17.10</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #1</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr"/>
-      <c r="H95" s="5" t="inlineStr">
-        <is>
-          <t>Крепыши 2</t>
-        </is>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>Анисимов</t>
-        </is>
-      </c>
-      <c r="J95" s="5" t="inlineStr">
-        <is>
-          <t>Профики</t>
-        </is>
-      </c>
-      <c r="K95" s="6" t="inlineStr">
-        <is>
-          <t>Беляев</t>
+      <c r="G95" s="10" t="inlineStr"/>
+      <c r="H95" s="11" t="inlineStr">
+        <is>
+          <t>Школа 35</t>
+        </is>
+      </c>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>Колюжный</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>Дружба</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="inlineStr">
+        <is>
+          <t>Майоров</t>
         </is>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>17.10</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
@@ -5580,50 +5597,50 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr"/>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>КС 26</t>
+          <t>68 школа</t>
         </is>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>Кузьмичев</t>
+          <t>Шкреба</t>
         </is>
       </c>
       <c r="J96" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Женя</t>
         </is>
       </c>
     </row>
     <row r="97" ht="16" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>17.10</t>
+          <t>11.10</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Пт</t>
+          <t>Сб</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
@@ -5639,132 +5656,128 @@
       <c r="G97" s="7" t="inlineStr"/>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>Дружба</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Смолкин</t>
         </is>
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>Школа 35</t>
+          <t>Школа 64/92</t>
         </is>
       </c>
       <c r="K97" s="9" t="inlineStr">
         <is>
-          <t>Колюжный</t>
+          <t>Тетерин</t>
         </is>
       </c>
     </row>
     <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>17.10</t>
         </is>
       </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C98" s="7" t="inlineStr">
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="D98" s="7" t="inlineStr">
-        <is>
-          <t>Поле 7*7</t>
-        </is>
-      </c>
-      <c r="E98" s="7" t="inlineStr">
-        <is>
-          <t>7*7</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr">
-        <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>Школа 139</t>
-        </is>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>Гурин</t>
-        </is>
-      </c>
-      <c r="J98" s="8" t="inlineStr">
-        <is>
-          <t>Смена-Ведиси</t>
-        </is>
-      </c>
-      <c r="K98" s="9" t="inlineStr">
-        <is>
-          <t>Куликов</t>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr"/>
+      <c r="H98" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J98" s="5" t="inlineStr">
+        <is>
+          <t>Профики</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="4" t="inlineStr">
+      <c r="A99" s="7" t="inlineStr">
         <is>
           <t>17.10</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C99" s="4" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #1</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>2020-2021 Предварительный 13 — 1 круг</t>
-        </is>
-      </c>
-      <c r="G99" s="4" t="inlineStr"/>
-      <c r="H99" s="5" t="inlineStr">
-        <is>
-          <t>Крепыши 2</t>
-        </is>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>Анисимов</t>
-        </is>
-      </c>
-      <c r="J99" s="5" t="inlineStr">
-        <is>
-          <t>Профики 2</t>
-        </is>
-      </c>
-      <c r="K99" s="6" t="inlineStr">
-        <is>
-          <t>Беляев</t>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C99" s="7" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #2</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>КС 26</t>
+        </is>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>Кузьмичев</t>
+        </is>
+      </c>
+      <c r="J99" s="8" t="inlineStr">
+        <is>
+          <t>Акулы 42/11</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="inlineStr">
+        <is>
+          <t>Щадин</t>
         </is>
       </c>
     </row>
@@ -5781,12 +5794,12 @@
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
@@ -5802,75 +5815,75 @@
       <c r="G100" s="7" t="inlineStr"/>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Дружба</t>
         </is>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J100" s="8" t="inlineStr">
         <is>
-          <t>Школа 16</t>
+          <t>Школа 35</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
-          <t>Смолкин</t>
+          <t>Колюжный</t>
         </is>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>17.10</t>
         </is>
       </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>18:30</t>
         </is>
       </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Поле 5*5 #3</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>2018-2019 Премьер 5×5 — 2 круга</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>Смена-Кошелев</t>
-        </is>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>Майоров</t>
-        </is>
-      </c>
-      <c r="J101" s="8" t="inlineStr">
-        <is>
-          <t>Комета</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr">
-        <is>
-          <t>Женя</t>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Поле 5*5 #1</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>2020-2021 Предварительный 13 — 1 круг</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr"/>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>Крепыши 2</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>Анисимов</t>
+        </is>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>Профики 2</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -5892,42 +5905,38 @@
       </c>
       <c r="D102" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
+          <t>2018-2019 Высшая 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="inlineStr"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>Уразаков</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J102" s="8" t="inlineStr">
         <is>
-          <t>Школа 139</t>
+          <t>Школа 16</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr">
         <is>
-          <t>Гурин</t>
+          <t>Смолкин</t>
         </is>
       </c>
     </row>
@@ -5944,12 +5953,12 @@
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #1</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E103" s="7" t="inlineStr">
@@ -5965,22 +5974,22 @@
       <c r="G103" s="7" t="inlineStr"/>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>Акулы 42/11</t>
+          <t>Смена-Кошелев</t>
         </is>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>Щадин</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J103" s="8" t="inlineStr">
         <is>
-          <t>Красные опасные</t>
+          <t>Комета</t>
         </is>
       </c>
       <c r="K103" s="9" t="inlineStr">
         <is>
-          <t>Анисимов</t>
+          <t>Женя</t>
         </is>
       </c>
     </row>
@@ -6002,7 +6011,7 @@
       </c>
       <c r="D104" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #2</t>
+          <t>Поле 5*5 #1</t>
         </is>
       </c>
       <c r="E104" s="7" t="inlineStr">
@@ -6018,22 +6027,22 @@
       <c r="G104" s="7" t="inlineStr"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>Смена-Кошелев</t>
+          <t>Акулы 42/11</t>
         </is>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>Майоров</t>
+          <t>Щадин</t>
         </is>
       </c>
       <c r="J104" s="8" t="inlineStr">
         <is>
-          <t>Профики</t>
+          <t>Красные опасные</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
         <is>
-          <t>Беляев</t>
+          <t>Анисимов</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6064,7 @@
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Поле 5*5 #3</t>
+          <t>Поле 5*5 #2</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
@@ -6071,22 +6080,22 @@
       <c r="G105" s="7" t="inlineStr"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>68 школа</t>
+          <t>Смена-Кошелев</t>
         </is>
       </c>
       <c r="I105" s="9" t="inlineStr">
         <is>
-          <t>Шкреба</t>
+          <t>Майоров</t>
         </is>
       </c>
       <c r="J105" s="8" t="inlineStr">
         <is>
-          <t>Спутник-1</t>
+          <t>Профики</t>
         </is>
       </c>
       <c r="K105" s="9" t="inlineStr">
         <is>
-          <t>Агарков</t>
+          <t>Беляев</t>
         </is>
       </c>
     </row>
@@ -6108,42 +6117,38 @@
       </c>
       <c r="D106" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 5*5 #3</t>
         </is>
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>7*7</t>
+          <t>5*5</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>2014-2015 Высшая 7×7 — группы 3×6</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>Группа C</t>
-        </is>
-      </c>
+          <t>2018-2019 Премьер 5×5 — 2 круга</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Смена-Ведиси</t>
+          <t>68 школа</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>Куликов</t>
+          <t>Шкреба</t>
         </is>
       </c>
       <c r="J106" s="8" t="inlineStr">
         <is>
-          <t>Крылья дубль-школа №7</t>
+          <t>Спутник-1</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr">
         <is>
-          <t>Уразаков</t>
+          <t>Агарков</t>
         </is>
       </c>
     </row>
@@ -10568,7 +10573,7 @@
       </c>
       <c r="D190" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E190" s="7" t="inlineStr">
@@ -12035,7 +12040,7 @@
       </c>
       <c r="D217" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E217" s="7" t="inlineStr">
@@ -12365,7 +12370,7 @@
       </c>
       <c r="D223" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E223" s="7" t="inlineStr">
@@ -12695,7 +12700,7 @@
       </c>
       <c r="D229" s="7" t="inlineStr">
         <is>
-          <t>Поле 7*7</t>
+          <t>Поле 7*7 #1</t>
         </is>
       </c>
       <c r="E229" s="7" t="inlineStr">
@@ -14389,9 +14394,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Конфликтов параллелей: 6 — есть!</t>
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Конфликтов параллелей: 0 — 0 ✓</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14515,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>2012-2013 7×7 16 ком 2кр (240 матчей) • 2014-2015 Премьер 7×7 2кр (56) • 2016-2017 Премьер 7×7 2кр (132) — итого 428 матчей 7×7, им нужен отдельный 7×7 фестиваль (не хватает 7×7 полей в этих датах)</t>
         </is>

--- a/Raspisanie_Osень_Fit.xlsx
+++ b/Raspisanie_Osень_Fit.xlsx
@@ -82,14 +82,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFBEB"/>
-        <bgColor rgb="00FFFBEB"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-        <bgColor rgb="00FEF3C7"/>
+        <fgColor rgb="00FFFBEB"/>
+        <bgColor rgb="00FFFBEB"/>
       </patternFill>
     </fill>
   </fills>
@@ -546,14 +546,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОСЕННИЙ БЛОК — РАСПИСАНИЕ С УЧЁТОМ ТРЕНЕРОВ (БЕЗ ПАРАЛЛЕЛЕЙ) • 60 мин слот</t>
+          <t>ОСЕННИЙ БЛОК — РАСПИСАНИЕ ТОЛЬКО НА ЭТИ 19 ДАТ (без января) • 2×7×7 везде • 60 мин слот</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Группы 2014 Высшая 3×6 (7×7) + Группы 2016 Высшая 5×4 (5×5) + 2018 Премьер/Высшая 5×5 2кр + 2020 предварительный 13 (5×5) — всего 299 матчей, все влезают в слоты</t>
+          <t>Группы 2014 Высшая 3×6 (7×7) + Группы 2016 Высшая 5×4 (5×5) + 2018 Премьер/Высшая 5×5 2кр + 2020 предварительный 13 (4×4 — отмечено) — всего 299 матчей, продолжение в январе</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F20" s="10" t="inlineStr">
@@ -1491,106 +1491,106 @@
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>27.08</t>
         </is>
       </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Ср</t>
         </is>
       </c>
-      <c r="C21" s="10" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F21" s="10" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J21" s="11" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr">
+      <c r="K21" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="10" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>27.08</t>
         </is>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Ср</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D22" s="10" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F22" s="10" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
       </c>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr">
+      <c r="K22" s="6" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F27" s="10" t="inlineStr">
@@ -1874,106 +1874,106 @@
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>27.08</t>
         </is>
       </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Ср</t>
         </is>
       </c>
-      <c r="C28" s="10" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D28" s="10" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F28" s="10" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G28" s="10" t="inlineStr"/>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J28" s="11" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K28" s="12" t="inlineStr">
+      <c r="K28" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>27.08</t>
         </is>
       </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Ср</t>
         </is>
       </c>
-      <c r="C29" s="10" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D29" s="10" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F29" s="10" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G29" s="10" t="inlineStr"/>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I29" s="12" t="inlineStr">
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J29" s="11" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="K29" s="12" t="inlineStr">
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F34" s="10" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -2310,53 +2310,53 @@
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="10" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>27.08</t>
         </is>
       </c>
-      <c r="B36" s="10" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Ср</t>
         </is>
       </c>
-      <c r="C36" s="10" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D36" s="10" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F36" s="10" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G36" s="10" t="inlineStr"/>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="I36" s="12" t="inlineStr">
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J36" s="11" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="K36" s="12" t="inlineStr">
+      <c r="K36" s="6" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="E83" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F83" s="10" t="inlineStr">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E84" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F84" s="10" t="inlineStr">
@@ -4987,53 +4987,53 @@
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B85" s="10" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C85" s="10" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D85" s="10" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E85" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F85" s="10" t="inlineStr">
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G85" s="10" t="inlineStr"/>
-      <c r="H85" s="11" t="inlineStr">
+      <c r="G85" s="4" t="inlineStr"/>
+      <c r="H85" s="5" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="I85" s="12" t="inlineStr">
+      <c r="I85" s="6" t="inlineStr">
         <is>
           <t>Тетерин</t>
         </is>
       </c>
-      <c r="J85" s="11" t="inlineStr">
+      <c r="J85" s="5" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr">
+      <c r="K85" s="6" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="E88" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F88" s="10" t="inlineStr">
@@ -5199,106 +5199,106 @@
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="10" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C89" s="10" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D89" s="10" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E89" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F89" s="10" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G89" s="10" t="inlineStr"/>
-      <c r="H89" s="11" t="inlineStr">
+      <c r="G89" s="4" t="inlineStr"/>
+      <c r="H89" s="5" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="I89" s="12" t="inlineStr">
+      <c r="I89" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J89" s="11" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="K89" s="12" t="inlineStr">
+      <c r="K89" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="10" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B90" s="10" t="inlineStr">
+      <c r="B90" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C90" s="10" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D90" s="10" t="inlineStr">
+      <c r="D90" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E90" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F90" s="10" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G90" s="10" t="inlineStr"/>
-      <c r="H90" s="11" t="inlineStr">
+      <c r="G90" s="4" t="inlineStr"/>
+      <c r="H90" s="5" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="I90" s="12" t="inlineStr">
+      <c r="I90" s="6" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
       </c>
-      <c r="J90" s="11" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="K90" s="12" t="inlineStr">
+      <c r="K90" s="6" t="inlineStr">
         <is>
           <t>Кузьмичев</t>
         </is>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="E93" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F93" s="10" t="inlineStr">
@@ -5464,106 +5464,106 @@
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="10" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B94" s="10" t="inlineStr">
+      <c r="B94" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C94" s="10" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D94" s="10" t="inlineStr">
+      <c r="D94" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E94" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F94" s="10" t="inlineStr">
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G94" s="10" t="inlineStr"/>
-      <c r="H94" s="11" t="inlineStr">
+      <c r="G94" s="4" t="inlineStr"/>
+      <c r="H94" s="5" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="I94" s="12" t="inlineStr">
+      <c r="I94" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J94" s="11" t="inlineStr">
+      <c r="J94" s="5" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="K94" s="12" t="inlineStr">
+      <c r="K94" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="10" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>11.10</t>
         </is>
       </c>
-      <c r="B95" s="10" t="inlineStr">
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C95" s="10" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D95" s="10" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E95" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F95" s="10" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G95" s="10" t="inlineStr"/>
-      <c r="H95" s="11" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr"/>
+      <c r="H95" s="5" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="I95" s="12" t="inlineStr">
+      <c r="I95" s="6" t="inlineStr">
         <is>
           <t>Колюжный</t>
         </is>
       </c>
-      <c r="J95" s="11" t="inlineStr">
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="K95" s="12" t="inlineStr">
+      <c r="K95" s="6" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
@@ -5698,7 +5698,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="E125" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F125" s="10" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="E126" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F126" s="10" t="inlineStr">
@@ -7213,53 +7213,53 @@
       </c>
     </row>
     <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="10" t="inlineStr">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>25.10</t>
         </is>
       </c>
-      <c r="B127" s="10" t="inlineStr">
+      <c r="B127" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C127" s="10" t="inlineStr">
+      <c r="C127" s="4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="D127" s="10" t="inlineStr">
+      <c r="D127" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E127" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F127" s="10" t="inlineStr">
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G127" s="10" t="inlineStr"/>
-      <c r="H127" s="11" t="inlineStr">
+      <c r="G127" s="4" t="inlineStr"/>
+      <c r="H127" s="5" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I127" s="12" t="inlineStr">
+      <c r="I127" s="6" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J127" s="11" t="inlineStr">
+      <c r="J127" s="5" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="K127" s="12" t="inlineStr">
+      <c r="K127" s="6" t="inlineStr">
         <is>
           <t>Цыганов</t>
         </is>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="E130" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F130" s="10" t="inlineStr">
@@ -7425,106 +7425,106 @@
       </c>
     </row>
     <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="10" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>25.10</t>
         </is>
       </c>
-      <c r="B131" s="10" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C131" s="10" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D131" s="10" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E131" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F131" s="10" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G131" s="10" t="inlineStr"/>
-      <c r="H131" s="11" t="inlineStr">
+      <c r="G131" s="4" t="inlineStr"/>
+      <c r="H131" s="5" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="I131" s="12" t="inlineStr">
+      <c r="I131" s="6" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
       </c>
-      <c r="J131" s="11" t="inlineStr">
+      <c r="J131" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K131" s="12" t="inlineStr">
+      <c r="K131" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="10" t="inlineStr">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>25.10</t>
         </is>
       </c>
-      <c r="B132" s="10" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C132" s="10" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>11:00</t>
         </is>
       </c>
-      <c r="D132" s="10" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E132" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F132" s="10" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G132" s="10" t="inlineStr"/>
-      <c r="H132" s="11" t="inlineStr">
+      <c r="G132" s="4" t="inlineStr"/>
+      <c r="H132" s="5" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="I132" s="12" t="inlineStr">
+      <c r="I132" s="6" t="inlineStr">
         <is>
           <t>Колюжный</t>
         </is>
       </c>
-      <c r="J132" s="11" t="inlineStr">
+      <c r="J132" s="5" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K132" s="12" t="inlineStr">
+      <c r="K132" s="6" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
@@ -7637,53 +7637,53 @@
       </c>
     </row>
     <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="10" t="inlineStr">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>25.10</t>
         </is>
       </c>
-      <c r="B135" s="10" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C135" s="10" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D135" s="10" t="inlineStr">
+      <c r="D135" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E135" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F135" s="10" t="inlineStr">
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G135" s="10" t="inlineStr"/>
-      <c r="H135" s="11" t="inlineStr">
+      <c r="G135" s="4" t="inlineStr"/>
+      <c r="H135" s="5" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="I135" s="12" t="inlineStr">
+      <c r="I135" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J135" s="11" t="inlineStr">
+      <c r="J135" s="5" t="inlineStr">
         <is>
           <t>Смена-Кошелев</t>
         </is>
       </c>
-      <c r="K135" s="12" t="inlineStr">
+      <c r="K135" s="6" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="E136" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F136" s="10" t="inlineStr">
@@ -7743,53 +7743,53 @@
       </c>
     </row>
     <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="10" t="inlineStr">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>25.10</t>
         </is>
       </c>
-      <c r="B137" s="10" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>Сб</t>
         </is>
       </c>
-      <c r="C137" s="10" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>12:00</t>
         </is>
       </c>
-      <c r="D137" s="10" t="inlineStr">
+      <c r="D137" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E137" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F137" s="10" t="inlineStr">
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G137" s="10" t="inlineStr"/>
-      <c r="H137" s="11" t="inlineStr">
+      <c r="G137" s="4" t="inlineStr"/>
+      <c r="H137" s="5" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="I137" s="12" t="inlineStr">
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>Женя</t>
         </is>
       </c>
-      <c r="J137" s="11" t="inlineStr">
+      <c r="J137" s="5" t="inlineStr">
         <is>
           <t>68 школа</t>
         </is>
       </c>
-      <c r="K137" s="12" t="inlineStr">
+      <c r="K137" s="6" t="inlineStr">
         <is>
           <t>Шкреба</t>
         </is>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -8538,159 +8538,159 @@
       </c>
     </row>
     <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="10" t="inlineStr">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B152" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C152" s="10" t="inlineStr">
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D152" s="10" t="inlineStr">
+      <c r="D152" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E152" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F152" s="10" t="inlineStr">
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F152" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G152" s="10" t="inlineStr"/>
-      <c r="H152" s="11" t="inlineStr">
+      <c r="G152" s="4" t="inlineStr"/>
+      <c r="H152" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="I152" s="12" t="inlineStr">
+      <c r="I152" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J152" s="11" t="inlineStr">
+      <c r="J152" s="5" t="inlineStr">
         <is>
           <t>Дружба</t>
         </is>
       </c>
-      <c r="K152" s="12" t="inlineStr">
+      <c r="K152" s="6" t="inlineStr">
         <is>
           <t>Майоров</t>
         </is>
       </c>
     </row>
     <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="10" t="inlineStr">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B153" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C153" s="10" t="inlineStr">
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D153" s="10" t="inlineStr">
+      <c r="D153" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E153" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F153" s="10" t="inlineStr">
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F153" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G153" s="10" t="inlineStr"/>
-      <c r="H153" s="11" t="inlineStr">
+      <c r="G153" s="4" t="inlineStr"/>
+      <c r="H153" s="5" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="I153" s="12" t="inlineStr">
+      <c r="I153" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
       </c>
-      <c r="J153" s="11" t="inlineStr">
+      <c r="J153" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K153" s="12" t="inlineStr">
+      <c r="K153" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="10" t="inlineStr">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B154" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C154" s="10" t="inlineStr">
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D154" s="10" t="inlineStr">
+      <c r="D154" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E154" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F154" s="10" t="inlineStr">
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F154" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G154" s="10" t="inlineStr"/>
-      <c r="H154" s="11" t="inlineStr">
+      <c r="G154" s="4" t="inlineStr"/>
+      <c r="H154" s="5" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="I154" s="12" t="inlineStr">
+      <c r="I154" s="6" t="inlineStr">
         <is>
           <t>Колюжный</t>
         </is>
       </c>
-      <c r="J154" s="11" t="inlineStr">
+      <c r="J154" s="5" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="K154" s="12" t="inlineStr">
+      <c r="K154" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
@@ -8719,7 +8719,7 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -8803,110 +8803,110 @@
       </c>
     </row>
     <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="10" t="inlineStr">
+      <c r="A157" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B157" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C157" s="10" t="inlineStr">
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D157" s="10" t="inlineStr">
+      <c r="D157" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E157" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F157" s="10" t="inlineStr">
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F157" s="4" t="inlineStr">
         <is>
           <t>2016-2017 Высшая 5×5 — группы 5×4</t>
         </is>
       </c>
-      <c r="G157" s="10" t="inlineStr">
+      <c r="G157" s="4" t="inlineStr">
         <is>
           <t>Группа B</t>
         </is>
       </c>
-      <c r="H157" s="11" t="inlineStr">
+      <c r="H157" s="5" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I157" s="12" t="inlineStr">
+      <c r="I157" s="6" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
-      <c r="J157" s="11" t="inlineStr">
+      <c r="J157" s="5" t="inlineStr">
         <is>
           <t>Огонь 3</t>
         </is>
       </c>
-      <c r="K157" s="12" t="inlineStr">
+      <c r="K157" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="10" t="inlineStr">
+      <c r="A158" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B158" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C158" s="10" t="inlineStr">
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D158" s="10" t="inlineStr">
+      <c r="D158" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E158" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F158" s="10" t="inlineStr">
+      <c r="E158" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F158" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G158" s="10" t="inlineStr"/>
-      <c r="H158" s="11" t="inlineStr">
+      <c r="G158" s="4" t="inlineStr"/>
+      <c r="H158" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I158" s="12" t="inlineStr">
+      <c r="I158" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J158" s="11" t="inlineStr">
+      <c r="J158" s="5" t="inlineStr">
         <is>
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="K158" s="12" t="inlineStr">
+      <c r="K158" s="6" t="inlineStr">
         <is>
           <t>Смолкин</t>
         </is>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="E159" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F159" s="10" t="inlineStr">
@@ -9072,159 +9072,159 @@
       </c>
     </row>
     <row r="162" ht="16" customHeight="1">
-      <c r="A162" s="10" t="inlineStr">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B162" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C162" s="10" t="inlineStr">
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D162" s="10" t="inlineStr">
+      <c r="D162" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E162" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F162" s="10" t="inlineStr">
+      <c r="E162" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F162" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G162" s="10" t="inlineStr"/>
-      <c r="H162" s="11" t="inlineStr">
+      <c r="G162" s="4" t="inlineStr"/>
+      <c r="H162" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="I162" s="12" t="inlineStr">
+      <c r="I162" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J162" s="11" t="inlineStr">
+      <c r="J162" s="5" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="K162" s="12" t="inlineStr">
+      <c r="K162" s="6" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
     </row>
     <row r="163" ht="16" customHeight="1">
-      <c r="A163" s="10" t="inlineStr">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B163" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C163" s="10" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D163" s="10" t="inlineStr">
+      <c r="D163" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E163" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F163" s="10" t="inlineStr">
+      <c r="E163" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F163" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G163" s="10" t="inlineStr"/>
-      <c r="H163" s="11" t="inlineStr">
+      <c r="G163" s="4" t="inlineStr"/>
+      <c r="H163" s="5" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="I163" s="12" t="inlineStr">
+      <c r="I163" s="6" t="inlineStr">
         <is>
           <t>Тетерин</t>
         </is>
       </c>
-      <c r="J163" s="11" t="inlineStr">
+      <c r="J163" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K163" s="12" t="inlineStr">
+      <c r="K163" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="164" ht="16" customHeight="1">
-      <c r="A164" s="10" t="inlineStr">
+      <c r="A164" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B164" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C164" s="10" t="inlineStr">
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D164" s="10" t="inlineStr">
+      <c r="D164" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E164" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F164" s="10" t="inlineStr">
+      <c r="E164" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F164" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G164" s="10" t="inlineStr"/>
-      <c r="H164" s="11" t="inlineStr">
+      <c r="G164" s="4" t="inlineStr"/>
+      <c r="H164" s="5" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="I164" s="12" t="inlineStr">
+      <c r="I164" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J164" s="11" t="inlineStr">
+      <c r="J164" s="5" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="K164" s="12" t="inlineStr">
+      <c r="K164" s="6" t="inlineStr">
         <is>
           <t>Колюжный</t>
         </is>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -9337,159 +9337,159 @@
       </c>
     </row>
     <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="10" t="inlineStr">
+      <c r="A167" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B167" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C167" s="10" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D167" s="10" t="inlineStr">
+      <c r="D167" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E167" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F167" s="10" t="inlineStr">
+      <c r="E167" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F167" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G167" s="10" t="inlineStr"/>
-      <c r="H167" s="11" t="inlineStr">
+      <c r="G167" s="4" t="inlineStr"/>
+      <c r="H167" s="5" t="inlineStr">
         <is>
           <t>Школа 1</t>
         </is>
       </c>
-      <c r="I167" s="12" t="inlineStr">
+      <c r="I167" s="6" t="inlineStr">
         <is>
           <t>Галимуллин</t>
         </is>
       </c>
-      <c r="J167" s="11" t="inlineStr">
+      <c r="J167" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="K167" s="12" t="inlineStr">
+      <c r="K167" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="168" ht="16" customHeight="1">
-      <c r="A168" s="10" t="inlineStr">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B168" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C168" s="10" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D168" s="10" t="inlineStr">
+      <c r="D168" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E168" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F168" s="10" t="inlineStr">
+      <c r="E168" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F168" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G168" s="10" t="inlineStr"/>
-      <c r="H168" s="11" t="inlineStr">
+      <c r="G168" s="4" t="inlineStr"/>
+      <c r="H168" s="5" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="I168" s="12" t="inlineStr">
+      <c r="I168" s="6" t="inlineStr">
         <is>
           <t>Кузьмичев</t>
         </is>
       </c>
-      <c r="J168" s="11" t="inlineStr">
+      <c r="J168" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K168" s="12" t="inlineStr">
+      <c r="K168" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
     </row>
     <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="10" t="inlineStr">
+      <c r="A169" s="4" t="inlineStr">
         <is>
           <t>07.11</t>
         </is>
       </c>
-      <c r="B169" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C169" s="10" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D169" s="10" t="inlineStr">
+      <c r="D169" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E169" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F169" s="10" t="inlineStr">
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G169" s="10" t="inlineStr"/>
-      <c r="H169" s="11" t="inlineStr">
+      <c r="G169" s="4" t="inlineStr"/>
+      <c r="H169" s="5" t="inlineStr">
         <is>
           <t>Акулы 42/11</t>
         </is>
       </c>
-      <c r="I169" s="12" t="inlineStr">
+      <c r="I169" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
       </c>
-      <c r="J169" s="11" t="inlineStr">
+      <c r="J169" s="5" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="K169" s="12" t="inlineStr">
+      <c r="K169" s="6" t="inlineStr">
         <is>
           <t>Женя</t>
         </is>
@@ -9571,7 +9571,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -10472,7 +10472,7 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
@@ -10992,114 +10992,114 @@
       </c>
     </row>
     <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="10" t="inlineStr">
+      <c r="A198" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B198" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C198" s="10" t="inlineStr">
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D198" s="10" t="inlineStr">
+      <c r="D198" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E198" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F198" s="10" t="inlineStr">
+      <c r="E198" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F198" s="4" t="inlineStr">
         <is>
           <t>2016-2017 Высшая 5×5 — группы 5×4</t>
         </is>
       </c>
-      <c r="G198" s="10" t="inlineStr">
+      <c r="G198" s="4" t="inlineStr">
         <is>
           <t>Группа D</t>
         </is>
       </c>
-      <c r="H198" s="11" t="inlineStr">
+      <c r="H198" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I198" s="12" t="inlineStr">
+      <c r="I198" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J198" s="11" t="inlineStr">
+      <c r="J198" s="5" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="K198" s="12" t="inlineStr">
+      <c r="K198" s="6" t="inlineStr">
         <is>
           <t>Женя</t>
         </is>
       </c>
     </row>
     <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="10" t="inlineStr">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B199" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C199" s="10" t="inlineStr">
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
         <is>
           <t>14:00</t>
         </is>
       </c>
-      <c r="D199" s="10" t="inlineStr">
+      <c r="D199" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E199" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F199" s="10" t="inlineStr">
+      <c r="E199" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F199" s="4" t="inlineStr">
         <is>
           <t>2016-2017 Высшая 5×5 — группы 5×4</t>
         </is>
       </c>
-      <c r="G199" s="10" t="inlineStr">
+      <c r="G199" s="4" t="inlineStr">
         <is>
           <t>Группа E</t>
         </is>
       </c>
-      <c r="H199" s="11" t="inlineStr">
+      <c r="H199" s="5" t="inlineStr">
         <is>
           <t>Красная фурия 2</t>
         </is>
       </c>
-      <c r="I199" s="12" t="inlineStr">
+      <c r="I199" s="6" t="inlineStr">
         <is>
           <t>Касьянов</t>
         </is>
       </c>
-      <c r="J199" s="11" t="inlineStr">
+      <c r="J199" s="5" t="inlineStr">
         <is>
           <t>Олимп 2</t>
         </is>
       </c>
-      <c r="K199" s="12" t="inlineStr">
+      <c r="K199" s="6" t="inlineStr">
         <is>
           <t>Щадин</t>
         </is>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -11234,7 +11234,7 @@
       </c>
       <c r="E202" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F202" s="10" t="inlineStr">
@@ -11265,106 +11265,106 @@
       </c>
     </row>
     <row r="203" ht="16" customHeight="1">
-      <c r="A203" s="10" t="inlineStr">
+      <c r="A203" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B203" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C203" s="10" t="inlineStr">
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="D203" s="10" t="inlineStr">
+      <c r="D203" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E203" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F203" s="10" t="inlineStr">
+      <c r="E203" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F203" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G203" s="10" t="inlineStr"/>
-      <c r="H203" s="11" t="inlineStr">
+      <c r="G203" s="4" t="inlineStr"/>
+      <c r="H203" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I203" s="12" t="inlineStr">
+      <c r="I203" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J203" s="11" t="inlineStr">
+      <c r="J203" s="5" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="K203" s="12" t="inlineStr">
+      <c r="K203" s="6" t="inlineStr">
         <is>
           <t>Женя</t>
         </is>
       </c>
     </row>
     <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="10" t="inlineStr">
+      <c r="A204" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B204" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C204" s="10" t="inlineStr">
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
         <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="D204" s="10" t="inlineStr">
+      <c r="D204" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #3</t>
         </is>
       </c>
-      <c r="E204" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F204" s="10" t="inlineStr">
+      <c r="E204" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F204" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G204" s="10" t="inlineStr"/>
-      <c r="H204" s="11" t="inlineStr">
+      <c r="G204" s="4" t="inlineStr"/>
+      <c r="H204" s="5" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="I204" s="12" t="inlineStr">
+      <c r="I204" s="6" t="inlineStr">
         <is>
           <t>Кузьмичев</t>
         </is>
       </c>
-      <c r="J204" s="11" t="inlineStr">
+      <c r="J204" s="5" t="inlineStr">
         <is>
           <t>Школа 35</t>
         </is>
       </c>
-      <c r="K204" s="12" t="inlineStr">
+      <c r="K204" s="6" t="inlineStr">
         <is>
           <t>Колюжный</t>
         </is>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -11503,7 +11503,7 @@
       </c>
       <c r="E207" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F207" s="10" t="inlineStr">
@@ -11534,53 +11534,53 @@
       </c>
     </row>
     <row r="208" ht="16" customHeight="1">
-      <c r="A208" s="10" t="inlineStr">
+      <c r="A208" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B208" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C208" s="10" t="inlineStr">
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
         <is>
           <t>16:00</t>
         </is>
       </c>
-      <c r="D208" s="10" t="inlineStr">
+      <c r="D208" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E208" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F208" s="10" t="inlineStr">
+      <c r="E208" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F208" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G208" s="10" t="inlineStr"/>
-      <c r="H208" s="11" t="inlineStr">
+      <c r="G208" s="4" t="inlineStr"/>
+      <c r="H208" s="5" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="I208" s="12" t="inlineStr">
+      <c r="I208" s="6" t="inlineStr">
         <is>
           <t>Цыганов</t>
         </is>
       </c>
-      <c r="J208" s="11" t="inlineStr">
+      <c r="J208" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K208" s="12" t="inlineStr">
+      <c r="K208" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -11609,7 +11609,7 @@
       </c>
       <c r="E209" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F209" s="10" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
@@ -11750,53 +11750,53 @@
       </c>
     </row>
     <row r="212" ht="16" customHeight="1">
-      <c r="A212" s="10" t="inlineStr">
+      <c r="A212" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B212" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C212" s="10" t="inlineStr">
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D212" s="10" t="inlineStr">
+      <c r="D212" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E212" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F212" s="10" t="inlineStr">
+      <c r="E212" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F212" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G212" s="10" t="inlineStr"/>
-      <c r="H212" s="11" t="inlineStr">
+      <c r="G212" s="4" t="inlineStr"/>
+      <c r="H212" s="5" t="inlineStr">
         <is>
           <t>Комета</t>
         </is>
       </c>
-      <c r="I212" s="12" t="inlineStr">
+      <c r="I212" s="6" t="inlineStr">
         <is>
           <t>Женя</t>
         </is>
       </c>
-      <c r="J212" s="11" t="inlineStr">
+      <c r="J212" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K212" s="12" t="inlineStr">
+      <c r="K212" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="E213" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F213" s="10" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="E214" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F214" s="10" t="inlineStr">
@@ -12080,53 +12080,53 @@
       </c>
     </row>
     <row r="218" ht="16" customHeight="1">
-      <c r="A218" s="10" t="inlineStr">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t>28.11</t>
         </is>
       </c>
-      <c r="B218" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C218" s="10" t="inlineStr">
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D218" s="10" t="inlineStr">
+      <c r="D218" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E218" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F218" s="10" t="inlineStr">
+      <c r="E218" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F218" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G218" s="10" t="inlineStr"/>
-      <c r="H218" s="11" t="inlineStr">
+      <c r="G218" s="4" t="inlineStr"/>
+      <c r="H218" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="I218" s="12" t="inlineStr">
+      <c r="I218" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
       </c>
-      <c r="J218" s="11" t="inlineStr">
+      <c r="J218" s="5" t="inlineStr">
         <is>
           <t>Молот</t>
         </is>
       </c>
-      <c r="K218" s="12" t="inlineStr">
+      <c r="K218" s="6" t="inlineStr">
         <is>
           <t>Цыганов</t>
         </is>
@@ -12155,7 +12155,7 @@
       </c>
       <c r="E219" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F219" s="10" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="E220" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F220" s="10" t="inlineStr">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="E224" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F224" s="10" t="inlineStr">
@@ -12485,7 +12485,7 @@
       </c>
       <c r="E225" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F225" s="10" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="E226" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F226" s="10" t="inlineStr">
@@ -12819,7 +12819,7 @@
       </c>
       <c r="E231" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F231" s="4" t="inlineStr">
@@ -12872,7 +12872,7 @@
       </c>
       <c r="E232" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F232" s="4" t="inlineStr">
@@ -12982,7 +12982,7 @@
       </c>
       <c r="E234" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F234" s="4" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="E235" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F235" s="4" t="inlineStr">
@@ -13145,7 +13145,7 @@
       </c>
       <c r="E237" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F237" s="4" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="E238" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F238" s="4" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="E240" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F240" s="4" t="inlineStr">
@@ -13357,7 +13357,7 @@
       </c>
       <c r="E241" s="4" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F241" s="4" t="inlineStr">
@@ -13388,53 +13388,53 @@
       </c>
     </row>
     <row r="242" ht="16" customHeight="1">
-      <c r="A242" s="10" t="inlineStr">
+      <c r="A242" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B242" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C242" s="10" t="inlineStr">
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D242" s="10" t="inlineStr">
+      <c r="D242" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E242" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F242" s="10" t="inlineStr">
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F242" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Премьер 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G242" s="10" t="inlineStr"/>
-      <c r="H242" s="11" t="inlineStr">
+      <c r="G242" s="4" t="inlineStr"/>
+      <c r="H242" s="5" t="inlineStr">
         <is>
           <t>Красные опасные</t>
         </is>
       </c>
-      <c r="I242" s="12" t="inlineStr">
+      <c r="I242" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J242" s="11" t="inlineStr">
+      <c r="J242" s="5" t="inlineStr">
         <is>
           <t>Спутник-1</t>
         </is>
       </c>
-      <c r="K242" s="12" t="inlineStr">
+      <c r="K242" s="6" t="inlineStr">
         <is>
           <t>Агарков</t>
         </is>
@@ -13463,7 +13463,7 @@
       </c>
       <c r="E243" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F243" s="10" t="inlineStr">
@@ -13516,7 +13516,7 @@
       </c>
       <c r="E244" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F244" s="10" t="inlineStr">
@@ -13547,53 +13547,53 @@
       </c>
     </row>
     <row r="245" ht="16" customHeight="1">
-      <c r="A245" s="10" t="inlineStr">
+      <c r="A245" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B245" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C245" s="10" t="inlineStr">
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D245" s="10" t="inlineStr">
+      <c r="D245" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E245" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F245" s="10" t="inlineStr">
+      <c r="E245" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F245" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G245" s="10" t="inlineStr"/>
-      <c r="H245" s="11" t="inlineStr">
+      <c r="G245" s="4" t="inlineStr"/>
+      <c r="H245" s="5" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="I245" s="12" t="inlineStr">
+      <c r="I245" s="6" t="inlineStr">
         <is>
           <t>Тетерин</t>
         </is>
       </c>
-      <c r="J245" s="11" t="inlineStr">
+      <c r="J245" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="K245" s="12" t="inlineStr">
+      <c r="K245" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="E246" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F246" s="10" t="inlineStr">
@@ -13653,53 +13653,53 @@
       </c>
     </row>
     <row r="247" ht="16" customHeight="1">
-      <c r="A247" s="10" t="inlineStr">
+      <c r="A247" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B247" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C247" s="10" t="inlineStr">
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D247" s="10" t="inlineStr">
+      <c r="D247" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E247" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F247" s="10" t="inlineStr">
+      <c r="E247" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F247" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G247" s="10" t="inlineStr"/>
-      <c r="H247" s="11" t="inlineStr">
+      <c r="G247" s="4" t="inlineStr"/>
+      <c r="H247" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="I247" s="12" t="inlineStr">
+      <c r="I247" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J247" s="11" t="inlineStr">
+      <c r="J247" s="5" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="K247" s="12" t="inlineStr">
+      <c r="K247" s="6" t="inlineStr">
         <is>
           <t>Кузьмичев</t>
         </is>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="E248" s="10" t="inlineStr">
         <is>
-          <t>5*5</t>
+          <t>4*4</t>
         </is>
       </c>
       <c r="F248" s="10" t="inlineStr">
@@ -13759,110 +13759,110 @@
       </c>
     </row>
     <row r="249" ht="16" customHeight="1">
-      <c r="A249" s="10" t="inlineStr">
+      <c r="A249" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B249" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C249" s="10" t="inlineStr">
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D249" s="10" t="inlineStr">
+      <c r="D249" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E249" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F249" s="10" t="inlineStr">
+      <c r="E249" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F249" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G249" s="10" t="inlineStr"/>
-      <c r="H249" s="11" t="inlineStr">
+      <c r="G249" s="4" t="inlineStr"/>
+      <c r="H249" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="I249" s="12" t="inlineStr">
+      <c r="I249" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J249" s="11" t="inlineStr">
+      <c r="J249" s="5" t="inlineStr">
         <is>
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="K249" s="12" t="inlineStr">
+      <c r="K249" s="6" t="inlineStr">
         <is>
           <t>Смолкин</t>
         </is>
       </c>
     </row>
     <row r="250" ht="16" customHeight="1">
-      <c r="A250" s="10" t="inlineStr">
+      <c r="A250" s="4" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="B250" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C250" s="10" t="inlineStr">
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D250" s="10" t="inlineStr">
+      <c r="D250" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #2</t>
         </is>
       </c>
-      <c r="E250" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F250" s="10" t="inlineStr">
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F250" s="4" t="inlineStr">
         <is>
           <t>2016-2017 Высшая 5×5 — группы 5×4</t>
         </is>
       </c>
-      <c r="G250" s="10" t="inlineStr">
+      <c r="G250" s="4" t="inlineStr">
         <is>
           <t>Группа D</t>
         </is>
       </c>
-      <c r="H250" s="11" t="inlineStr">
+      <c r="H250" s="5" t="inlineStr">
         <is>
           <t>Барсы</t>
         </is>
       </c>
-      <c r="I250" s="12" t="inlineStr">
+      <c r="I250" s="6" t="inlineStr">
         <is>
           <t>Седин</t>
         </is>
       </c>
-      <c r="J250" s="11" t="inlineStr">
+      <c r="J250" s="5" t="inlineStr">
         <is>
           <t>Профики</t>
         </is>
       </c>
-      <c r="K250" s="12" t="inlineStr">
+      <c r="K250" s="6" t="inlineStr">
         <is>
           <t>Беляев</t>
         </is>
@@ -14138,212 +14138,212 @@
       </c>
     </row>
     <row r="256" ht="16" customHeight="1">
-      <c r="A256" s="10" t="inlineStr">
+      <c r="A256" s="4" t="inlineStr">
         <is>
           <t>26.12</t>
         </is>
       </c>
-      <c r="B256" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C256" s="10" t="inlineStr">
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="D256" s="10" t="inlineStr">
+      <c r="D256" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E256" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F256" s="10" t="inlineStr">
+      <c r="E256" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F256" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G256" s="10" t="inlineStr"/>
-      <c r="H256" s="11" t="inlineStr">
+      <c r="G256" s="4" t="inlineStr"/>
+      <c r="H256" s="5" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="I256" s="12" t="inlineStr">
+      <c r="I256" s="6" t="inlineStr">
         <is>
           <t>Кузьмичев</t>
         </is>
       </c>
-      <c r="J256" s="11" t="inlineStr">
+      <c r="J256" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 2</t>
         </is>
       </c>
-      <c r="K256" s="12" t="inlineStr">
+      <c r="K256" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="257" ht="16" customHeight="1">
-      <c r="A257" s="10" t="inlineStr">
+      <c r="A257" s="4" t="inlineStr">
         <is>
           <t>26.12</t>
         </is>
       </c>
-      <c r="B257" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C257" s="10" t="inlineStr">
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="D257" s="10" t="inlineStr">
+      <c r="D257" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E257" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F257" s="10" t="inlineStr">
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F257" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G257" s="10" t="inlineStr"/>
-      <c r="H257" s="11" t="inlineStr">
+      <c r="G257" s="4" t="inlineStr"/>
+      <c r="H257" s="5" t="inlineStr">
         <is>
           <t>Школа 16</t>
         </is>
       </c>
-      <c r="I257" s="12" t="inlineStr">
+      <c r="I257" s="6" t="inlineStr">
         <is>
           <t>Смолкин</t>
         </is>
       </c>
-      <c r="J257" s="11" t="inlineStr">
+      <c r="J257" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="K257" s="12" t="inlineStr">
+      <c r="K257" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="258" ht="16" customHeight="1">
-      <c r="A258" s="10" t="inlineStr">
+      <c r="A258" s="4" t="inlineStr">
         <is>
           <t>26.12</t>
         </is>
       </c>
-      <c r="B258" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C258" s="10" t="inlineStr">
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
         <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="D258" s="10" t="inlineStr">
+      <c r="D258" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E258" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F258" s="10" t="inlineStr">
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F258" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G258" s="10" t="inlineStr"/>
-      <c r="H258" s="11" t="inlineStr">
+      <c r="G258" s="4" t="inlineStr"/>
+      <c r="H258" s="5" t="inlineStr">
         <is>
           <t>Школа 64/92</t>
         </is>
       </c>
-      <c r="I258" s="12" t="inlineStr">
+      <c r="I258" s="6" t="inlineStr">
         <is>
           <t>Тетерин</t>
         </is>
       </c>
-      <c r="J258" s="11" t="inlineStr">
+      <c r="J258" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="K258" s="12" t="inlineStr">
+      <c r="K258" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
     </row>
     <row r="259" ht="16" customHeight="1">
-      <c r="A259" s="10" t="inlineStr">
+      <c r="A259" s="4" t="inlineStr">
         <is>
           <t>26.12</t>
         </is>
       </c>
-      <c r="B259" s="10" t="inlineStr">
-        <is>
-          <t>Пт</t>
-        </is>
-      </c>
-      <c r="C259" s="10" t="inlineStr">
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Пт</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
         <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="D259" s="10" t="inlineStr">
+      <c r="D259" s="4" t="inlineStr">
         <is>
           <t>Поле 4*4 #1</t>
         </is>
       </c>
-      <c r="E259" s="10" t="inlineStr">
-        <is>
-          <t>5*5</t>
-        </is>
-      </c>
-      <c r="F259" s="10" t="inlineStr">
+      <c r="E259" s="4" t="inlineStr">
+        <is>
+          <t>5*5</t>
+        </is>
+      </c>
+      <c r="F259" s="4" t="inlineStr">
         <is>
           <t>2018-2019 Высшая 5×5 — 2 круга</t>
         </is>
       </c>
-      <c r="G259" s="10" t="inlineStr"/>
-      <c r="H259" s="11" t="inlineStr">
+      <c r="G259" s="4" t="inlineStr"/>
+      <c r="H259" s="5" t="inlineStr">
         <is>
           <t>Красные опасные 3</t>
         </is>
       </c>
-      <c r="I259" s="12" t="inlineStr">
+      <c r="I259" s="6" t="inlineStr">
         <is>
           <t>Анисимов</t>
         </is>
       </c>
-      <c r="J259" s="11" t="inlineStr">
+      <c r="J259" s="5" t="inlineStr">
         <is>
           <t>КС 26</t>
         </is>
       </c>
-      <c r="K259" s="12" t="inlineStr">
+      <c r="K259" s="6" t="inlineStr">
         <is>
           <t>Кузьмичев</t>
         </is>
